--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
@@ -1369,21 +1369,17 @@
       </c>
       <c r="M3" s="8" t="str"/>
       <c r="N3" s="8" t="str"/>
-      <c r="O3" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O3" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P3" s="80" t="inlineStr">
         <is>
-          <t>第4章1に基本理念と3つの基本目標がある。地域包括ケアの将来像は第6章11・12に分かれて書かれている</t>
-        </is>
-      </c>
-      <c r="Q3" s="80" t="inlineStr">
-        <is>
-          <t>第4章1に「本町の地域包括ケアの姿」を1段落で定義し、第6章11・12から参照する</t>
-        </is>
-      </c>
+          <t>第4章1に「本町の地域包括ケアの姿」を定義（第12版）。第6章11・12から参照</t>
+        </is>
+      </c>
+      <c r="Q3" s="80" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -1696,7 +1692,7 @@
       </c>
       <c r="P7" s="80" t="inlineStr">
         <is>
-          <t>第1章5で町全域を1圏域とし理由を記載。面積・交通（町営バス・デマンド交通）の数値は町データ待ち（確認事項№44）</t>
+          <t>第1章5で町全域を1圏域とし理由を記載。面積・交通（町営バス・デマンド交通）の数値は町データ待ち（確認事項№44、素案に印あり）</t>
         </is>
       </c>
       <c r="Q7" s="80" t="inlineStr">
@@ -2032,7 +2028,7 @@
       </c>
       <c r="P11" s="80" t="inlineStr">
         <is>
-          <t>第5章の各施策と資料編8（成果指標48件の定義）。目標値は協議会で設定（未確定55か所）</t>
+          <t>第5章の各施策に成果指標48件、資料編8に定義と種類の一覧。目標値は協議会で設定（【協議会で設定】56か所）</t>
         </is>
       </c>
       <c r="Q11" s="80" t="inlineStr">
@@ -2431,12 +2427,12 @@
       </c>
       <c r="P16" s="80" t="inlineStr">
         <is>
-          <t>県保健医療計画（第八次）の在宅医療・病床を反映済み。医療計画との整合は3課長連名通知による要請と書き分け済み。新たな地域医療構想（令和9年度以降）は未反映</t>
+          <t>県保健医療計画（第八次）を反映済み。第12版で、令和9年4月1日から地域医療構想が医療計画とは別の県の構想に改まること（改正後の医療法第30条の3の3）を第1章3に記載</t>
         </is>
       </c>
       <c r="Q16" s="80" t="inlineStr">
         <is>
-          <t>新たな地域医療構想の県の方針が示された段階で追記</t>
+          <t>県の新たな地域医療構想が示された段階で第5章 基本目標2⑦に反映</t>
         </is>
       </c>
     </row>
@@ -2728,21 +2724,17 @@
       </c>
       <c r="M20" s="8" t="str"/>
       <c r="N20" s="8" t="str"/>
-      <c r="O20" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O20" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P20" s="80" t="inlineStr">
         <is>
-          <t>一体的実施は第5章基本目標1①。健康増進計画・認知症関連計画との役割分担の表がない</t>
-        </is>
-      </c>
-      <c r="Q20" s="80" t="inlineStr">
-        <is>
-          <t>第4章3の関連計画の表に健康増進計画の行を足す</t>
-        </is>
-      </c>
+          <t>第4章3に保健・認知症の分野の関連計画（健康増進計画・特定健診等実施計画・一体的実施・市町村認知症施策推進計画）との役割分担の表を追加（第12版）。計画名・期間は町データ待ち</t>
+        </is>
+      </c>
+      <c r="Q20" s="80" t="n"/>
     </row>
     <row r="21" ht="62" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -2893,7 +2885,7 @@
       </c>
       <c r="P22" s="80" t="inlineStr">
         <is>
-          <t>令和7年8月8日の第10期調査説明会資料は当方未取得（厚生労働省サイトは当方の環境から不通）。調査は国の様式で令和7年度に実施済み</t>
+          <t>令和7年8月8日の第10期調査説明会資料は当方未取得。調査は国の様式で令和7年度に実施済み</t>
         </is>
       </c>
       <c r="Q22" s="80" t="inlineStr">
@@ -3537,12 +3529,12 @@
       </c>
       <c r="P30" s="80" t="inlineStr">
         <is>
-          <t>協議会での検討を前提に記載。庁内ワーキングの体制と開催予定の記載がない</t>
+          <t>第1章7に庁内の検討体制と関係する担当の表を追加（第12版）。会議の名称・構成・開催予定は町の決定待ち</t>
         </is>
       </c>
       <c r="Q30" s="80" t="inlineStr">
         <is>
-          <t>第1章7に庁内体制と開催予定を書く</t>
+          <t>町が庁内会議の名称・構成・開催予定を決めた段階で第1章7に記入</t>
         </is>
       </c>
     </row>
@@ -3609,21 +3601,17 @@
       </c>
       <c r="M31" s="8" t="str"/>
       <c r="N31" s="8" t="str"/>
-      <c r="O31" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O31" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P31" s="80" t="inlineStr">
         <is>
-          <t>協議会・関係団体ヒアリングを記載。住宅部門の参画は記載がない</t>
-        </is>
-      </c>
-      <c r="Q31" s="80" t="inlineStr">
-        <is>
-          <t>住宅担当の関与を第1章7に書く</t>
-        </is>
-      </c>
+          <t>協議会・関係団体ヒアリングに加え、第1章7に住宅担当の関与（有料老人ホーム・サ高住の入居定員、県の居住安定確保計画、公営住宅）を記載（第12版）</t>
+        </is>
+      </c>
+      <c r="Q31" s="80" t="n"/>
     </row>
     <row r="32" ht="62" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -3763,21 +3751,17 @@
       </c>
       <c r="M33" s="8" t="str"/>
       <c r="N33" s="8" t="str"/>
-      <c r="O33" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O33" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P33" s="80" t="inlineStr">
         <is>
-          <t>成果指標48件の定義はあるが、アウトプット指標とアウトカム指標の区分を表示していない</t>
-        </is>
-      </c>
-      <c r="Q33" s="80" t="inlineStr">
-        <is>
-          <t>資料編8に指標の種類（アウトプット／アウトカム）の列を足す</t>
-        </is>
-      </c>
+          <t>資料編8に成果指標48件の種類の一覧（アウトプット30件・アウトカム18件）を追加（第12版）。生成のたびに第5章の表から拾い、種類のない指標があれば止める</t>
+        </is>
+      </c>
+      <c r="Q33" s="80" t="n"/>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -4723,19 +4707,19 @@
           <t>https://www.mhlw.go.jp/stf/shingi2/0000138653_00007.html</t>
         </is>
       </c>
-      <c r="O45" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O45" s="82" t="inlineStr">
+        <is>
+          <t>資料徴求中</t>
         </is>
       </c>
       <c r="P45" s="80" t="inlineStr">
         <is>
-          <t>第2章2（2）。認定データとの連携の仕様は報告書で確認していない</t>
+          <t>第2章2（2）。報告書（原本）に認定データとの連携の記載がなく、個票も未受領のため確かめられない</t>
         </is>
       </c>
       <c r="Q45" s="80" t="inlineStr">
         <is>
-          <t>報告書で認定データ連携の有無を確認</t>
+          <t>個票の受領時に認定データとの連携の有無を町に確認（素案の確認事項に追加）</t>
         </is>
       </c>
     </row>
@@ -5213,9 +5197,9 @@
           <t>https://www.mhlw.go.jp/stf/shingi2/0000138653_00007.html</t>
         </is>
       </c>
-      <c r="O51" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O51" s="82" t="inlineStr">
+        <is>
+          <t>資料徴求中</t>
         </is>
       </c>
       <c r="P51" s="80" t="inlineStr">
@@ -5225,7 +5209,7 @@
       </c>
       <c r="Q51" s="80" t="inlineStr">
         <is>
-          <t>地域ケア会議の資料を依頼</t>
+          <t>地域ケア会議の資料を依頼（素案の確認事項に追加）</t>
         </is>
       </c>
     </row>
@@ -6132,12 +6116,12 @@
       </c>
       <c r="P63" s="80" t="inlineStr">
         <is>
-          <t>総合事業は第5章基本目標1②。新たなガイドラインとの照合は未了</t>
+          <t>総合事業は第5章基本目標1②。第12版でガイドラインと照合して確定する旨を記載。照合は未了</t>
         </is>
       </c>
       <c r="Q63" s="80" t="inlineStr">
         <is>
-          <t>ガイドラインと実施方針を照合</t>
+          <t>国のガイドラインの最新版と実施方針を照合</t>
         </is>
       </c>
     </row>
@@ -6279,14 +6263,14 @@
       </c>
       <c r="M65" s="8" t="str"/>
       <c r="N65" s="8" t="str"/>
-      <c r="O65" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O65" s="82" t="inlineStr">
+        <is>
+          <t>資料徴求中</t>
         </is>
       </c>
       <c r="P65" s="80" t="inlineStr">
         <is>
-          <t>重層的支援体制整備事業は第3期地域福祉計画が担うと整理。実施の有無は未確認</t>
+          <t>重層的支援体制整備事業は第3期地域福祉計画が担うと整理。本町での実施の有無は町に照会（第12版で第1章2に印）</t>
         </is>
       </c>
       <c r="Q65" s="80" t="inlineStr">
@@ -6989,7 +6973,7 @@
       </c>
       <c r="P74" s="80" t="inlineStr">
         <is>
-          <t>介護度別と認知症高齢者の日常生活自立度を記載。自立度IIIa・IIIbの値が未受領</t>
+          <t>介護度別と認知症高齢者の日常生活自立度を記載。自立度IIIa・IIIbの値が未受領（見える化Ｂ7の出力で確定と素案に記載）</t>
         </is>
       </c>
       <c r="Q74" s="80" t="inlineStr">
@@ -8542,14 +8526,14 @@
       </c>
       <c r="M94" s="8" t="str"/>
       <c r="N94" s="8" t="str"/>
-      <c r="O94" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O94" s="82" t="inlineStr">
+        <is>
+          <t>資料徴求中</t>
         </is>
       </c>
       <c r="P94" s="80" t="inlineStr">
         <is>
-          <t>基金のメニューと県の交付要綱は未確認</t>
+          <t>第12版で、基金のメニューと県の交付要綱を県に確認中である旨を第5章 基本目標2⑥に記載</t>
         </is>
       </c>
       <c r="Q94" s="80" t="inlineStr">
@@ -8621,14 +8605,14 @@
       </c>
       <c r="M95" s="8" t="str"/>
       <c r="N95" s="8" t="str"/>
-      <c r="O95" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O95" s="82" t="inlineStr">
+        <is>
+          <t>資料徴求中</t>
         </is>
       </c>
       <c r="P95" s="80" t="inlineStr">
         <is>
-          <t>ICT・介護テクノロジーの導入を記載。ケアプランデータ連携の導入状況は未把握</t>
+          <t>ICT・介護テクノロジーとケアプランデータ連携システムの導入支援を記載（第12版）。町内事業所の導入状況は未把握</t>
         </is>
       </c>
       <c r="Q95" s="80" t="inlineStr">
@@ -8775,19 +8759,19 @@
       </c>
       <c r="M97" s="8" t="str"/>
       <c r="N97" s="8" t="str"/>
-      <c r="O97" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O97" s="84" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="P97" s="80" t="inlineStr">
         <is>
-          <t>人材の指標は採用以外（定着率・稼働率）を置いていない</t>
+          <t>第12版で、第5章 基本目標2⑥に介護職員の定着（町内事業所の離職率）の指標を追加。現状値の把握方法は協議会で決める</t>
         </is>
       </c>
       <c r="Q97" s="80" t="inlineStr">
         <is>
-          <t>成果指標に定着の指標を足すか協議</t>
+          <t>離職率の把握方法（事業所への照会等）を協議会で決める</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
@@ -161,12 +161,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -2878,21 +2878,17 @@
           <t>https://www.mhlw.go.jp/stf/newpage_74620.html</t>
         </is>
       </c>
-      <c r="O22" s="83" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="O22" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P22" s="80" t="inlineStr">
         <is>
-          <t>令和7年8月8日の第10期調査説明会資料は当方未取得。調査は国の様式で令和7年度に実施済み</t>
-        </is>
-      </c>
-      <c r="Q22" s="80" t="inlineStr">
-        <is>
-          <t>資料の提供を依頼</t>
-        </is>
-      </c>
+          <t>令和7年8月8日の第10期調査説明会資料（資料1〜5）を取得（令和8年10月20日）。ニーズ調査・在宅介護実態調査は国の様式で令和7年度に実施済み</t>
+        </is>
+      </c>
+      <c r="Q22" s="80" t="n"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -2961,19 +2957,19 @@
           <t>https://www.mhlw.go.jp/stf/newpage_74620.html</t>
         </is>
       </c>
-      <c r="O23" s="83" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="O23" s="81" t="inlineStr">
+        <is>
+          <t>確認中</t>
         </is>
       </c>
       <c r="P23" s="80" t="inlineStr">
         <is>
-          <t>令和8年3月11日の全国担当課長会議資料は当方未取得</t>
+          <t>令和8年3月の全国担当課長会議資料を取得し照合。所得段階の年金収入等の基準額が82.65万円に改正済みで、素案の80万円は誤り</t>
         </is>
       </c>
       <c r="Q23" s="80" t="inlineStr">
         <is>
-          <t>資料の提供を依頼</t>
+          <t>第5章③の所得段階の表を82.65万円に改める</t>
         </is>
       </c>
     </row>
@@ -3044,19 +3040,19 @@
           <t>https://www.mhlw.go.jp/stf/newpage_74620.html</t>
         </is>
       </c>
-      <c r="O24" s="83" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="O24" s="81" t="inlineStr">
+        <is>
+          <t>確認中</t>
         </is>
       </c>
       <c r="P24" s="80" t="inlineStr">
         <is>
-          <t>令和8年7月15日の全国介護保険担当課長会議資料は当方未取得。保険料算定・調整交付金に関わるため優先度が高い</t>
+          <t>令和8年7月15日の全国介護保険担当課長会議資料を取得し照合。基本指針の告示は令和8年11月の予定（素案は令和9年1月）。特定地域で本町は振興山村の一部指定として掲載。標準段階・補正係数・改定率は未提示</t>
         </is>
       </c>
       <c r="Q24" s="80" t="inlineStr">
         <is>
-          <t>資料3-1・3-2の提供を依頼</t>
+          <t>照合結果と修正対応方針（№2〜10）に沿って第13版に反映</t>
         </is>
       </c>
     </row>
@@ -3127,19 +3123,19 @@
           <t>https://www.mhlw.go.jp/stf/newpage_74620.html</t>
         </is>
       </c>
-      <c r="O25" s="83" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="O25" s="81" t="inlineStr">
+        <is>
+          <t>確認中</t>
         </is>
       </c>
       <c r="P25" s="80" t="inlineStr">
         <is>
-          <t>令和8年9月の地域分析手引き改訂版は当方未取得</t>
+          <t>令和8年9月改訂版の地域分析の手引きを取得し照合。別表1の指標のうち介護SCRと死亡場所別の死亡数が素案にない</t>
         </is>
       </c>
       <c r="Q25" s="80" t="inlineStr">
         <is>
-          <t>資料の提供を依頼</t>
+          <t>資料編5に別表1の指標の一覧を置く</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3822,7 @@
       </c>
       <c r="M34" s="8" t="str"/>
       <c r="N34" s="8" t="str"/>
-      <c r="O34" s="84" t="inlineStr">
+      <c r="O34" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -3905,7 +3901,7 @@
       </c>
       <c r="M35" s="8" t="str"/>
       <c r="N35" s="8" t="str"/>
-      <c r="O35" s="83" t="inlineStr">
+      <c r="O35" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -4790,7 +4786,7 @@
           <t>https://www.mhlw.go.jp/stf/shingi2/0000138653_00007.html</t>
         </is>
       </c>
-      <c r="O46" s="84" t="inlineStr">
+      <c r="O46" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -4873,7 +4869,7 @@
           <t>https://www.mhlw.go.jp/stf/shingi2/0000138653_00007.html</t>
         </is>
       </c>
-      <c r="O47" s="84" t="inlineStr">
+      <c r="O47" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -4956,7 +4952,7 @@
           <t>https://www.mhlw.go.jp/stf/shingi2/0000138653_00007.html</t>
         </is>
       </c>
-      <c r="O48" s="84" t="inlineStr">
+      <c r="O48" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -5505,7 +5501,7 @@
       </c>
       <c r="M55" s="8" t="str"/>
       <c r="N55" s="8" t="str"/>
-      <c r="O55" s="84" t="inlineStr">
+      <c r="O55" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -5734,7 +5730,7 @@
       </c>
       <c r="M58" s="8" t="str"/>
       <c r="N58" s="8" t="str"/>
-      <c r="O58" s="83" t="inlineStr">
+      <c r="O58" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -5809,7 +5805,7 @@
       </c>
       <c r="M59" s="8" t="str"/>
       <c r="N59" s="8" t="str"/>
-      <c r="O59" s="83" t="inlineStr">
+      <c r="O59" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -6725,7 +6721,7 @@
           <t>https://www.mhlw.go.jp/content/12301000/001751471.pdf</t>
         </is>
       </c>
-      <c r="O71" s="83" t="inlineStr">
+      <c r="O71" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -7432,7 +7428,7 @@
       </c>
       <c r="M80" s="8" t="str"/>
       <c r="N80" s="8" t="str"/>
-      <c r="O80" s="84" t="inlineStr">
+      <c r="O80" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -7511,7 +7507,7 @@
       </c>
       <c r="M81" s="8" t="str"/>
       <c r="N81" s="8" t="str"/>
-      <c r="O81" s="83" t="inlineStr">
+      <c r="O81" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -8684,7 +8680,7 @@
       </c>
       <c r="M96" s="8" t="str"/>
       <c r="N96" s="8" t="str"/>
-      <c r="O96" s="83" t="inlineStr">
+      <c r="O96" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -8759,7 +8755,7 @@
       </c>
       <c r="M97" s="8" t="str"/>
       <c r="N97" s="8" t="str"/>
-      <c r="O97" s="84" t="inlineStr">
+      <c r="O97" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -9063,7 +9059,7 @@
       </c>
       <c r="M101" s="8" t="str"/>
       <c r="N101" s="8" t="str"/>
-      <c r="O101" s="83" t="inlineStr">
+      <c r="O101" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -9442,7 +9438,7 @@
       </c>
       <c r="M106" s="8" t="str"/>
       <c r="N106" s="8" t="str"/>
-      <c r="O106" s="83" t="inlineStr">
+      <c r="O106" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -10117,7 +10113,7 @@
       </c>
       <c r="M115" s="8" t="str"/>
       <c r="N115" s="8" t="str"/>
-      <c r="O115" s="83" t="inlineStr">
+      <c r="O115" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -10516,7 +10512,7 @@
           <t>https://kouseikyoku.mhlw.go.jp/kantoshinetsu/000409256.pdf</t>
         </is>
       </c>
-      <c r="O120" s="83" t="inlineStr">
+      <c r="O120" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -10678,7 +10674,7 @@
           <t>https://kouseikyoku.mhlw.go.jp/kantoshinetsu/000409256.pdf</t>
         </is>
       </c>
-      <c r="O122" s="83" t="inlineStr">
+      <c r="O122" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -10761,7 +10757,7 @@
           <t>https://kouseikyoku.mhlw.go.jp/kantoshinetsu/000409256.pdf</t>
         </is>
       </c>
-      <c r="O123" s="83" t="inlineStr">
+      <c r="O123" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -11819,7 +11815,7 @@
       </c>
       <c r="M137" s="8" t="str"/>
       <c r="N137" s="8" t="str"/>
-      <c r="O137" s="84" t="inlineStr">
+      <c r="O137" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -11969,7 +11965,7 @@
       </c>
       <c r="M139" s="8" t="str"/>
       <c r="N139" s="8" t="str"/>
-      <c r="O139" s="84" t="inlineStr">
+      <c r="O139" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
@@ -12719,7 +12715,7 @@
       </c>
       <c r="M149" s="8" t="str"/>
       <c r="N149" s="8" t="str"/>
-      <c r="O149" s="83" t="inlineStr">
+      <c r="O149" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -12944,7 +12940,7 @@
       </c>
       <c r="M152" s="8" t="str"/>
       <c r="N152" s="8" t="str"/>
-      <c r="O152" s="83" t="inlineStr">
+      <c r="O152" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -13493,7 +13489,7 @@
           <t>https://www.mhlw.go.jp/stf/newpage_17090.html</t>
         </is>
       </c>
-      <c r="O159" s="83" t="inlineStr">
+      <c r="O159" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -13888,7 +13884,7 @@
           <t>https://www.mhlw.go.jp/stf/newpage_17527.html</t>
         </is>
       </c>
-      <c r="O164" s="83" t="inlineStr">
+      <c r="O164" s="84" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -14662,7 +14658,7 @@
       </c>
       <c r="M174" s="8" t="str"/>
       <c r="N174" s="8" t="str"/>
-      <c r="O174" s="84" t="inlineStr">
+      <c r="O174" s="83" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_第10期_策定チェックリスト_確認結果_20261020.xlsx
@@ -2957,21 +2957,17 @@
           <t>https://www.mhlw.go.jp/stf/newpage_74620.html</t>
         </is>
       </c>
-      <c r="O23" s="81" t="inlineStr">
-        <is>
-          <t>確認中</t>
+      <c r="O23" s="79" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="P23" s="80" t="inlineStr">
         <is>
-          <t>令和8年3月の全国担当課長会議資料を取得し照合。所得段階の年金収入等の基準額が82.65万円に改正済みで、素案の80万円は誤り</t>
-        </is>
-      </c>
-      <c r="Q23" s="80" t="inlineStr">
-        <is>
-          <t>第5章③の所得段階の表を82.65万円に改める</t>
-        </is>
-      </c>
+          <t>令和8年3月の全国担当課長会議資料を取得し照合。所得段階の年金収入等の基準額（82.65万円への政令改正）を第13版に反映</t>
+        </is>
+      </c>
+      <c r="Q23" s="80" t="n"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -3047,12 +3043,12 @@
       </c>
       <c r="P24" s="80" t="inlineStr">
         <is>
-          <t>令和8年7月15日の全国介護保険担当課長会議資料を取得し照合。基本指針の告示は令和8年11月の予定（素案は令和9年1月）。特定地域で本町は振興山村の一部指定として掲載。標準段階・補正係数・改定率は未提示</t>
+          <t>令和8年7月15日の全国介護保険担当課長会議資料を取得し照合。基本指針の告示は令和8年11月の予定（素案は令和9年1月）。特定地域で本町は振興山村の一部指定として掲載。標準段階・補正係数・改定率は未提示。告示時期・特定地域・拠点事業・身寄りの相談は第13版に反映</t>
         </is>
       </c>
       <c r="Q24" s="80" t="inlineStr">
         <is>
-          <t>照合結果と修正対応方針（№2〜10）に沿って第13版に反映</t>
+          <t>標準段階・調整交付金の補正係数の提示後に保険料を再算定。入居定員総数を県に照会</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3126,12 @@
       </c>
       <c r="P25" s="80" t="inlineStr">
         <is>
-          <t>令和8年9月改訂版の地域分析の手引きを取得し照合。別表1の指標のうち介護SCRと死亡場所別の死亡数が素案にない</t>
+          <t>令和8年9月改訂版の地域分析の手引きを取得し照合。基本指針の案の別表1の指標と本計画の対応を資料編12に置いた（第13版）。介護SCRと死亡場所別の死亡数は見える化出力待ち</t>
         </is>
       </c>
       <c r="Q25" s="80" t="inlineStr">
         <is>
-          <t>資料編5に別表1の指標の一覧を置く</t>
+          <t>見える化システムから介護SCRと死亡場所別の死亡数を出力する</t>
         </is>
       </c>
     </row>
